--- a/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/DuomenysTestui/visi_zive_irasai_atrankai._modif_v1 - Darb - testui.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/DuomenysTestui/visi_zive_irasai_atrankai._modif_v1 - Darb - testui.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AtsisiuntimasZiveDuomenu\DuomenysTestui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F88DAF6-2F6A-460B-8995-CE0C9F284FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3671BBDB-C443-431D-B8DC-7730F9D8E424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1900" windowWidth="19200" windowHeight="7710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="18600" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="84">
   <si>
     <t>filename</t>
   </si>
@@ -90,12 +90,6 @@
     <t>60f9188487cf66240e3780bf</t>
   </si>
   <si>
-    <t>1001_3</t>
-  </si>
-  <si>
-    <t>60f9188487cf6678b43780c3</t>
-  </si>
-  <si>
     <t>1001_2</t>
   </si>
   <si>
@@ -171,9 +165,6 @@
     <t>1626931.201</t>
   </si>
   <si>
-    <t>1626933.71</t>
-  </si>
-  <si>
     <t>1626924.927</t>
   </si>
   <si>
@@ -289,9 +280,6 @@
   </si>
   <si>
     <t>izolinija šokinėja nedaug, vietomis išlenda raumenų triušmai. Kokybė nebloga, žymėjimas koreguotas, gana daug triukšminių intervalų, gal geriau tinka testavimui</t>
-  </si>
-  <si>
-    <t>BW nedidelis, bet nuolatinis, yra ryškių EMG epizodų. Kokybė nebloga, žymėjimas koreguotas, tačiau nors triukšmai pažymėti, bet vis tiek dar išlenda silpni raumenų triukšmai, mokymui nerekomenduojamas</t>
   </si>
   <si>
     <t>Neaišku, kas yra ties 12300 klausimas gydytojui. Gal verta užblokuoti 3 pūpsnius pradedant reikšme 68100, gal dar 2 - ties 92700, nors dabartiniam ML nepakenkė. Kokybė nebloga, žymėjimas koreguotas , tačiau nors triukšmai pažymėti, bet vis tiek dar išlenda silpni raumenų triukšmai, mokymui nerekomenduojamas</t>
@@ -741,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="13.6328125" style="13" customWidth="1"/>
@@ -773,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>5</v>
@@ -788,55 +776,55 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="V1" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>7</v>
@@ -845,18 +833,18 @@
         <v>6</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>127999</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -868,7 +856,7 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I2" s="8">
         <v>861</v>
@@ -913,27 +901,27 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="X2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z2" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>575999</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -990,27 +978,27 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="X3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>908799</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1067,27 +1055,27 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y4" t="s">
         <v>10</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>127999</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1144,27 +1132,27 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="X5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Y5" t="s">
         <v>10</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>127999</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1176,7 +1164,7 @@
         <v>2222</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I6" s="8">
         <v>746</v>
@@ -1221,54 +1209,54 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="s">
         <v>10</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B7">
-        <v>127999</v>
+        <v>115199</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>2222</v>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I7" s="8">
-        <v>869</v>
+        <v>764</v>
       </c>
       <c r="J7" s="8">
-        <v>865</v>
+        <v>761</v>
       </c>
       <c r="K7" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" s="15">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="16">
         <v>0</v>
@@ -1280,13 +1268,13 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="S7" s="9">
-        <v>6.4063000492191353</v>
+        <v>0</v>
       </c>
       <c r="T7" s="8">
         <v>0</v>
@@ -1298,54 +1286,54 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="X7" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="Y7" t="s">
         <v>10</v>
       </c>
-      <c r="Z7" s="5" t="s">
-        <v>85</v>
+      <c r="Z7" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>115199</v>
+        <v>127999</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>8</v>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>2222</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I8" s="8">
-        <v>764</v>
+        <v>806</v>
       </c>
       <c r="J8" s="8">
-        <v>761</v>
+        <v>805</v>
       </c>
       <c r="K8" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="15">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="16">
         <v>0</v>
@@ -1357,13 +1345,13 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4480</v>
       </c>
       <c r="S8" s="9">
-        <v>0</v>
+        <v>3.5000273439636249</v>
       </c>
       <c r="T8" s="8">
         <v>0</v>
@@ -1375,72 +1363,72 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="X8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="s">
         <v>10</v>
       </c>
-      <c r="Z8" s="6" t="s">
-        <v>37</v>
+      <c r="Z8" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>127999</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>44</v>
+        <v>128000</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>2222</v>
+        <v>1111</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I9" s="8">
-        <v>806</v>
+        <v>720</v>
       </c>
       <c r="J9" s="8">
-        <v>805</v>
+        <v>718</v>
       </c>
       <c r="K9" s="16">
+        <v>0</v>
+      </c>
+      <c r="L9" s="15">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="16">
+        <v>0</v>
+      </c>
+      <c r="O9" s="15">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
         <v>1</v>
       </c>
-      <c r="L9" s="15">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" s="16">
-        <v>0</v>
-      </c>
-      <c r="O9" s="15">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>5</v>
-      </c>
       <c r="R9">
-        <v>4480</v>
+        <v>300</v>
       </c>
       <c r="S9" s="9">
-        <v>3.5000273439636249</v>
+        <v>0.234375</v>
       </c>
       <c r="T9" s="8">
         <v>0</v>
@@ -1452,72 +1440,69 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y9" t="s">
         <v>10</v>
       </c>
-      <c r="Z9" s="5" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>128000</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>43</v>
+      <c r="C10" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>1111</v>
+        <v>2222</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="I10" s="8">
-        <v>720</v>
+        <v>801</v>
       </c>
       <c r="J10" s="8">
-        <v>718</v>
+        <v>798</v>
       </c>
       <c r="K10" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" s="15">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" s="16">
+        <v>0</v>
+      </c>
+      <c r="O10" s="15">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
         <v>2</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" s="16">
-        <v>0</v>
-      </c>
-      <c r="O10" s="15">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
       <c r="R10">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="S10" s="9">
-        <v>0.234375</v>
+        <v>0.34375</v>
       </c>
       <c r="T10" s="8">
         <v>0</v>
@@ -1529,49 +1514,52 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="s">
         <v>10</v>
       </c>
+      <c r="Z10" s="5" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>128000</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>41</v>
+      <c r="C11" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1111</v>
+      </c>
+      <c r="H11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="8">
+        <v>739</v>
+      </c>
+      <c r="J11" s="8">
+        <v>737</v>
+      </c>
+      <c r="K11" s="16">
+        <v>0</v>
+      </c>
+      <c r="L11" s="15">
         <v>2</v>
       </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>2222</v>
-      </c>
-      <c r="H11" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="8">
-        <v>801</v>
-      </c>
-      <c r="J11" s="8">
-        <v>798</v>
-      </c>
-      <c r="K11" s="16">
-        <v>3</v>
-      </c>
-      <c r="L11" s="15">
-        <v>0</v>
-      </c>
       <c r="M11">
         <v>0</v>
       </c>
@@ -1585,13 +1573,13 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>440</v>
+        <v>600</v>
       </c>
       <c r="S11" s="9">
-        <v>0.34375</v>
+        <v>0.46875</v>
       </c>
       <c r="T11" s="8">
         <v>0</v>
@@ -1603,52 +1591,49 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="s">
         <v>10</v>
       </c>
-      <c r="Z11" s="5" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B12">
-        <v>128000</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>42</v>
+        <v>127999</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="8">
+        <v>604</v>
+      </c>
+      <c r="J12" s="8">
+        <v>603</v>
+      </c>
+      <c r="K12" s="16">
+        <v>0</v>
+      </c>
+      <c r="L12" s="15">
         <v>1</v>
       </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1111</v>
-      </c>
-      <c r="H12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="8">
-        <v>739</v>
-      </c>
-      <c r="J12" s="8">
-        <v>737</v>
-      </c>
-      <c r="K12" s="16">
-        <v>0</v>
-      </c>
-      <c r="L12" s="15">
-        <v>2</v>
-      </c>
       <c r="M12">
         <v>0</v>
       </c>
@@ -1662,13 +1647,13 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="S12" s="9">
-        <v>0.46875</v>
+        <v>0</v>
       </c>
       <c r="T12" s="8">
         <v>0</v>
@@ -1680,92 +1665,18 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X12" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="Y12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13">
-        <v>127999</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="8">
-        <v>604</v>
-      </c>
-      <c r="J13" s="8">
-        <v>603</v>
-      </c>
-      <c r="K13" s="16">
-        <v>0</v>
-      </c>
-      <c r="L13" s="15">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" s="16">
-        <v>0</v>
-      </c>
-      <c r="O13" s="15">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13" s="9">
-        <v>0</v>
-      </c>
-      <c r="T13" s="8">
-        <v>0</v>
-      </c>
-      <c r="U13" s="8">
-        <v>0</v>
-      </c>
-      <c r="V13" s="10">
-        <v>0</v>
-      </c>
-      <c r="W13" t="s">
-        <v>64</v>
-      </c>
-      <c r="X13" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z13">
-    <sortCondition ref="A2:A13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z12">
+    <sortCondition ref="A2:A12"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1779,7 +1690,7 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.35">
@@ -1787,7 +1698,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.35">
@@ -1795,7 +1706,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.35">
@@ -1803,7 +1714,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.35">
@@ -1811,7 +1722,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.35">
@@ -1819,15 +1730,15 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
